--- a/output/pdf_financials_xlsx/PNP.xlsx
+++ b/output/pdf_financials_xlsx/PNP.xlsx
@@ -1793,7 +1793,7 @@
         <v>157.393</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>297.643</v>
+        <v>-297.643</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-298.341</v>
@@ -2012,7 +2012,7 @@
         <v>157.393</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>297.643</v>
+        <v>-297.643</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-298.341</v>
@@ -6551,25 +6551,25 @@
         <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-0.039</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.036</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="L91" s="3" t="n">
         <v>0</v>
@@ -6982,7 +6982,7 @@
         <v>157.393</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>297.643</v>
+        <v>-297.643</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-298.341</v>
@@ -13380,7 +13380,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -16478,7 +16482,11 @@
           <t>Foreign currency translation reserve (35)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -22190,7 +22198,11 @@
           <t>Foreign currency translation reserve (22)</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -40050,7 +40062,7 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>297.643</v>
+        <v>-297.643</v>
       </c>
       <c r="H299" s="5" t="n">
         <v>-298.341</v>
@@ -57944,7 +57956,7 @@
         </is>
       </c>
       <c r="G470" s="5" t="n">
-        <v>297.643</v>
+        <v>-297.643</v>
       </c>
       <c r="H470" s="5" t="n">
         <v>-298.341</v>

--- a/output/pdf_financials_xlsx/PNP.xlsx
+++ b/output/pdf_financials_xlsx/PNP.xlsx
@@ -8616,7 +8616,7 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.953</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -8681,7 +8681,7 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.953</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -43924,7 +43924,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -53008,7 +53012,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
